--- a/Tools/excel2json/excel/SkillDefine.xlsx
+++ b/Tools/excel2json/excel/SkillDefine.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="89">
   <si>
     <t>ID</t>
   </si>
@@ -229,6 +229,9 @@
     <t>Attack</t>
   </si>
   <si>
+    <t>Effects/Hits/Holy hit</t>
+  </si>
+  <si>
     <t>[0.5]</t>
   </si>
   <si>
@@ -262,7 +265,7 @@
     <t>[1]</t>
   </si>
   <si>
-    <t>火灵咒</t>
+    <t>木棍戳戳</t>
   </si>
   <si>
     <t>法师的基础法术，无消耗</t>
@@ -271,10 +274,10 @@
     <t>Prefabs/UI/Icon/skill_icon_001_2001</t>
   </si>
   <si>
-    <t>Missile/missile_2001</t>
-  </si>
-  <si>
-    <t>南明离火</t>
+    <t>[0]</t>
+  </si>
+  <si>
+    <t>火球术</t>
   </si>
   <si>
     <t>对单体目标造成法术伤害</t>
@@ -283,7 +286,16 @@
     <t>Prefabs/UI/Icon/skill_icon_001_2002</t>
   </si>
   <si>
-    <t>点</t>
+    <t>Intonate</t>
+  </si>
+  <si>
+    <t>Effects/Fly/FireBall</t>
+  </si>
+  <si>
+    <t>Effects/Hits/Explosion</t>
+  </si>
+  <si>
+    <t>[0.2]</t>
   </si>
 </sst>
 </file>
@@ -914,7 +926,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -927,6 +939,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1577,11 +1592,14 @@
       <c r="S4" s="3">
         <v>0</v>
       </c>
+      <c r="T4" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="U4" s="3">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X4" s="3">
         <v>0</v>
@@ -1656,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X5" s="3">
         <v>30</v>
@@ -1731,7 +1749,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X6" s="3">
         <v>60</v>
@@ -1758,10 +1776,10 @@
         <v>1002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
@@ -1770,7 +1788,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>63</v>
@@ -1791,7 +1809,7 @@
         <v>20</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P7" s="3">
         <v>5</v>
@@ -1806,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X7" s="3">
         <v>150</v>
@@ -1833,10 +1851,10 @@
         <v>1002</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" s="3">
         <v>1</v>
@@ -1845,13 +1863,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>63</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K8" s="3">
         <v>3.5</v>
@@ -1866,7 +1884,7 @@
         <v>25</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P8" s="3">
         <v>10</v>
@@ -1881,10 +1899,10 @@
         <v>4000</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X8" s="3">
         <v>100</v>
@@ -1911,10 +1929,10 @@
         <v>2001</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F9" s="3">
         <v>1</v>
@@ -1926,7 +1944,7 @@
         <v>62</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>64</v>
@@ -1935,7 +1953,7 @@
         <v>1.5</v>
       </c>
       <c r="L9" s="3">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="M9" s="3">
         <v>0.9</v>
@@ -1950,19 +1968,17 @@
         <v>0</v>
       </c>
       <c r="Q9" s="3">
-        <v>1</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="S9" s="3">
-        <v>8000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T9" s="5"/>
       <c r="U9" s="3">
         <v>0</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="X9" s="3">
         <v>0</v>
@@ -1989,10 +2005,10 @@
         <v>2002</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F10" s="3">
         <v>1</v>
@@ -2001,19 +2017,19 @@
         <v>1</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="K10" s="3">
         <v>5</v>
       </c>
       <c r="L10" s="3">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="M10" s="3">
         <v>1.5</v>
@@ -2022,7 +2038,7 @@
         <v>35</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="P10" s="3">
         <v>5</v>
@@ -2031,16 +2047,19 @@
         <v>1</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="S10" s="3">
-        <v>10000</v>
+        <v>15000</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="U10" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="X10" s="3">
         <v>0</v>

--- a/Tools/excel2json/excel/SkillDefine.xlsx
+++ b/Tools/excel2json/excel/SkillDefine.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="97">
   <si>
     <t>ID</t>
   </si>
@@ -71,7 +71,10 @@
     <t>Cost</t>
   </si>
   <si>
-    <t>AnimName</t>
+    <t>IntonateAnimName</t>
+  </si>
+  <si>
+    <t>ActiveAnimName</t>
   </si>
   <si>
     <t>ReqLevel</t>
@@ -92,6 +95,12 @@
     <t>Area</t>
   </si>
   <si>
+    <t>Duration</t>
+  </si>
+  <si>
+    <t>Interval</t>
+  </si>
+  <si>
     <t>HitDelay</t>
   </si>
   <si>
@@ -170,7 +179,10 @@
     <t>魔法消耗</t>
   </si>
   <si>
-    <t>施法动作</t>
+    <t>前摇动作</t>
+  </si>
+  <si>
+    <t>激活动作</t>
   </si>
   <si>
     <t>等级要求</t>
@@ -189,6 +201,12 @@
   </si>
   <si>
     <t>影响区域</t>
+  </si>
+  <si>
+    <t>整个技能的持续时间</t>
+  </si>
+  <si>
+    <t>伤害间隔</t>
   </si>
   <si>
     <t>命中时间，动作开始到命中</t>
@@ -226,7 +244,7 @@
     <t>单位</t>
   </si>
   <si>
-    <t>Attack</t>
+    <t>Attack01</t>
   </si>
   <si>
     <t>Effects/Hits/Holy hit</t>
@@ -296,6 +314,12 @@
   </si>
   <si>
     <t>[0.2]</t>
+  </si>
+  <si>
+    <t>野怪近战[物理]</t>
+  </si>
+  <si>
+    <t>野怪通用近战</t>
   </si>
 </sst>
 </file>
@@ -1262,7 +1286,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1277,17 +1301,20 @@
     <col min="10" max="10" width="38.15" style="3" customWidth="1"/>
     <col min="11" max="12" width="10.775" style="3" customWidth="1"/>
     <col min="13" max="13" width="15.65" style="3" customWidth="1"/>
-    <col min="14" max="16" width="10.775" style="3" customWidth="1"/>
-    <col min="17" max="18" width="18.075" style="3" customWidth="1"/>
-    <col min="19" max="19" width="14.8583333333333" style="3" customWidth="1"/>
-    <col min="20" max="20" width="21.575" style="3" customWidth="1"/>
-    <col min="21" max="21" width="10.775" style="3" customWidth="1"/>
-    <col min="22" max="22" width="24.4333333333333" style="3" customWidth="1"/>
-    <col min="23" max="24" width="10.775" style="3" customWidth="1"/>
-    <col min="25" max="16384" width="9" style="3"/>
+    <col min="14" max="14" width="10.775" style="3" customWidth="1"/>
+    <col min="15" max="15" width="23.475" style="3" customWidth="1"/>
+    <col min="16" max="16" width="22.925" style="3" customWidth="1"/>
+    <col min="17" max="17" width="10.775" style="3" customWidth="1"/>
+    <col min="18" max="19" width="18.075" style="3" customWidth="1"/>
+    <col min="20" max="20" width="14.8583333333333" style="3" customWidth="1"/>
+    <col min="21" max="21" width="21.575" style="3" customWidth="1"/>
+    <col min="22" max="22" width="10.775" style="3" customWidth="1"/>
+    <col min="23" max="25" width="24.4333333333333" style="3" customWidth="1"/>
+    <col min="26" max="27" width="10.775" style="3" customWidth="1"/>
+    <col min="28" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:27">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:30">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1369,177 +1396,203 @@
       <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:27">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:30">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>32</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="59" customHeight="1" spans="1:27">
+    <row r="3" s="2" customFormat="1" ht="59" customHeight="1" spans="1:30">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC3" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:27">
+    <row r="4" customHeight="1" spans="1:30">
       <c r="A4" s="3">
-        <f>ROW()</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -1548,10 +1601,10 @@
         <v>1001</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F4" s="3">
         <v>1</v>
@@ -1560,13 +1613,13 @@
         <v>3</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K4" s="3">
         <v>1.5</v>
@@ -1581,73 +1634,81 @@
         <v>0</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="P4" s="3">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="Q4" s="3">
         <v>0</v>
       </c>
-      <c r="S4" s="3">
-        <v>0</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="U4" s="3">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>67</v>
+      <c r="R4" s="3">
+        <v>0</v>
+      </c>
+      <c r="T4" s="3">
+        <v>0</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="V4" s="3">
+        <v>0</v>
+      </c>
+      <c r="W4" s="3">
+        <v>0.85</v>
       </c>
       <c r="X4" s="3">
         <v>0</v>
       </c>
-      <c r="Y4" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z4" s="3">
+      <c r="Y4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="3">
         <v>1</v>
       </c>
-      <c r="AA4" s="3">
+      <c r="AD4" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:27">
+    <row r="5" customHeight="1" spans="1:30">
       <c r="A5" s="3">
-        <f t="shared" ref="A5:A17" si="0">ROW()</f>
+        <v>2</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1002</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K5" s="3">
         <v>5</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1001</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" s="3">
-        <v>2</v>
-      </c>
-      <c r="G5" s="3">
-        <v>3</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="K5" s="3">
-        <v>1.5</v>
       </c>
       <c r="L5" s="3">
         <v>3500</v>
@@ -1656,130 +1717,149 @@
         <v>0</v>
       </c>
       <c r="N5" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="P5" s="3">
-        <v>0</v>
+        <v>77</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="Q5" s="3">
-        <v>0</v>
-      </c>
-      <c r="S5" s="3">
-        <v>0</v>
-      </c>
-      <c r="U5" s="3">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>67</v>
+        <v>5</v>
+      </c>
+      <c r="R5" s="3">
+        <v>0</v>
+      </c>
+      <c r="T5" s="3">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3">
+        <v>0</v>
+      </c>
+      <c r="W5" s="3">
+        <v>0</v>
       </c>
       <c r="X5" s="3">
-        <v>30</v>
-      </c>
-      <c r="Y5" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA5" s="3">
+        <v>150</v>
+      </c>
+      <c r="AB5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="3">
         <v>1</v>
       </c>
-      <c r="AA5" s="3">
+      <c r="AD5" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:27">
+    <row r="6" customHeight="1" spans="1:30">
       <c r="A6" s="3">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="F6" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="K6" s="3">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="L6" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="M6" s="3">
         <v>0</v>
       </c>
       <c r="N6" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="P6" s="3">
-        <v>0</v>
+        <v>81</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="Q6" s="3">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3">
-        <v>0</v>
-      </c>
-      <c r="U6" s="3">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="s">
-        <v>67</v>
+        <v>10</v>
+      </c>
+      <c r="R6" s="3">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W6" s="3">
+        <v>0</v>
       </c>
       <c r="X6" s="3">
-        <v>60</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:30">
+      <c r="A7" s="3">
+        <v>101</v>
+      </c>
+      <c r="B7" s="3">
         <v>1</v>
       </c>
-      <c r="AA6" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:27">
-      <c r="A7" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0</v>
-      </c>
       <c r="C7" s="3">
-        <v>1002</v>
+        <v>2001</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
@@ -1788,73 +1868,82 @@
         <v>1</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="K7" s="3">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="L7" s="3">
         <v>3500</v>
       </c>
       <c r="M7" s="3">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="N7" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="P7" s="3">
-        <v>5</v>
+      <c r="P7" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="Q7" s="3">
         <v>0</v>
       </c>
-      <c r="S7" s="3">
-        <v>0</v>
-      </c>
-      <c r="U7" s="3">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="s">
-        <v>67</v>
+      <c r="R7" s="3">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5"/>
+      <c r="V7" s="3">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3">
+        <v>0</v>
       </c>
       <c r="X7" s="3">
-        <v>150</v>
-      </c>
-      <c r="Y7" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="AD7" s="3">
         <v>1</v>
       </c>
-      <c r="AA7" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" customHeight="1" spans="1:27">
+    <row r="8" customHeight="1" spans="1:30">
       <c r="A8" s="3">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="B8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="3">
-        <v>1002</v>
+        <v>2002</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="F8" s="3">
         <v>1</v>
@@ -1863,76 +1952,87 @@
         <v>1</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="K8" s="3">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="L8" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="M8" s="3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N8" s="3">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="P8" s="3">
-        <v>10</v>
+        <v>91</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-      <c r="U8" s="3">
+        <v>5</v>
+      </c>
+      <c r="R8" s="3">
+        <v>1</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="T8" s="3">
+        <v>15000</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="V8" s="3">
         <v>4000</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>77</v>
+      <c r="W8" s="3">
+        <v>0</v>
       </c>
       <c r="X8" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>0.8</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
       </c>
+      <c r="AB8" s="3">
+        <v>250</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" customHeight="1" spans="1:27">
+    <row r="9" customHeight="1" spans="1:30">
       <c r="A9" s="3">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <v>1001</v>
       </c>
       <c r="B9" s="3">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="C9" s="3">
-        <v>2001</v>
+        <v>101</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="F9" s="3">
         <v>1</v>
@@ -1941,137 +2041,67 @@
         <v>1</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K9" s="3">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="L9" s="3">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="M9" s="3">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="N9" s="3">
         <v>0</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="P9" s="3">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="Q9" s="3">
         <v>0</v>
       </c>
-      <c r="S9" s="3">
-        <v>0</v>
-      </c>
-      <c r="T9" s="5"/>
-      <c r="U9" s="3">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>81</v>
+      <c r="R9" s="3">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3">
+        <v>0</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="V9" s="3">
+        <v>0</v>
+      </c>
+      <c r="W9" s="3">
+        <v>0.85</v>
       </c>
       <c r="X9" s="3">
         <v>0</v>
       </c>
-      <c r="Y9" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>1.2</v>
+      <c r="Y9" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="AA9" s="3">
+        <v>50</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:27">
-      <c r="A10" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B10" s="3">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3">
-        <v>2002</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="K10" s="3">
-        <v>5</v>
-      </c>
-      <c r="L10" s="3">
-        <v>30000</v>
-      </c>
-      <c r="M10" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="N10" s="3">
-        <v>35</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="P10" s="3">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>1</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="S10" s="3">
-        <v>15000</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="U10" s="3">
-        <v>4000</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="X10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>250</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>1</v>
+      <c r="AD9" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Tools/excel2json/excel/SkillDefine.xlsx
+++ b/Tools/excel2json/excel/SkillDefine.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="97">
   <si>
     <t>ID</t>
   </si>
@@ -203,7 +203,8 @@
     <t>影响区域</t>
   </si>
   <si>
-    <t>整个技能的持续时间</t>
+    <t>整个技能的持续时间,
+也就是激活状态持续的时间</t>
   </si>
   <si>
     <t>伤害间隔</t>
@@ -244,7 +245,10 @@
     <t>单位</t>
   </si>
   <si>
-    <t>Attack01</t>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Attack</t>
   </si>
   <si>
     <t>Effects/Hits/Holy hit</t>
@@ -269,9 +273,6 @@
   </si>
   <si>
     <t>对自身周围造成范围伤害</t>
-  </si>
-  <si>
-    <t>None</t>
   </si>
   <si>
     <t>SpellB</t>
@@ -1565,7 +1566,7 @@
       <c r="V3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W3" s="4" t="s">
         <v>58</v>
       </c>
       <c r="X3" s="2" t="s">
@@ -1637,7 +1638,7 @@
         <v>71</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q4" s="3">
         <v>0</v>
@@ -1649,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="V4" s="3">
         <v>0</v>
@@ -1661,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AA4" s="3">
         <v>0</v>
@@ -1687,10 +1688,10 @@
         <v>1002</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -1699,7 +1700,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>69</v>
@@ -1720,10 +1721,10 @@
         <v>20</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q5" s="3">
         <v>5</v>
@@ -1744,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AA5" s="3">
         <v>150</v>
@@ -1770,10 +1771,10 @@
         <v>1003</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F6" s="3">
         <v>1</v>
@@ -1782,13 +1783,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="K6" s="3">
         <v>3.5</v>
@@ -1803,7 +1804,7 @@
         <v>25</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="P6" s="3" t="s">
         <v>81</v>
@@ -1883,7 +1884,7 @@
         <v>3500</v>
       </c>
       <c r="M7" s="3">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="N7" s="3">
         <v>0</v>
@@ -1892,7 +1893,7 @@
         <v>71</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q7" s="3">
         <v>0</v>
@@ -1903,12 +1904,14 @@
       <c r="T7" s="3">
         <v>0</v>
       </c>
-      <c r="U7" s="5"/>
+      <c r="U7" s="5" t="s">
+        <v>73</v>
+      </c>
       <c r="V7" s="3">
         <v>0</v>
       </c>
       <c r="W7" s="3">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="X7" s="3">
         <v>0</v>
@@ -1952,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>90</v>
@@ -1976,7 +1979,7 @@
         <v>91</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="Q8" s="3">
         <v>5</v>
@@ -2065,7 +2068,7 @@
         <v>71</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q9" s="3">
         <v>0</v>
@@ -2077,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="V9" s="3">
         <v>0</v>
@@ -2089,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AA9" s="3">
         <v>50</v>
